--- a/csv/官網數據紀錄檔/文章排名追蹤.xlsx
+++ b/csv/官網數據紀錄檔/文章排名追蹤.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-07" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-09" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2261,4 +2262,1372 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>數據更新時間</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>觀察時間範圍</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28天(2026-08-30~2026-09-26)；全站 97點擊/4,310曝光/CTR 2.2%/平均排名10.6。列出全部有曝光的36篇文章</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>上架時間</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>文章ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>文章類型(依標題推測非官方標籤)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>核心關鍵字(依標題推測非官方紀錄)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>點擊</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>曝光</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>文章問題備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>foundation-skintype-guide-2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>粉底液推薦</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1433</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>主力頁面；佔全站曝光33.2%(9/24為33.6%)，集中度幾乎沒降。9/17優化窗口已涵蓋10天：點擊35→39、排名(頁面)12.7。最大字「混合肌 粉底液」排10.0，乾肌/油肌推薦字仍在36~42名</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>department-store-anniversary-sale-guide</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>資訊懶人包</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>百貨週年慶檔期</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>491</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>曝光357→491升至全站第2；查詢字分散(21個多為1次曝光)，「台中新光三越週年慶2026」排1.0並帶進點擊；CTR 3.08%→2.65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>eye-lip-remover-irritation-guide</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>眼唇卸妝液刺痛</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>381</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.36%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9/24決定不動、維持觀察；排名5.3。可見查詢字只剩2個(「为什么卸妆后眼皮刺痛」16曝光)，其餘仍是低於GSC顯示門檻的長尾查詢</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cleansing-balm-emulsify-guide</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>卸妝膏怎麼用</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>278</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>點擊5→7、CTR 1.87%→2.52%回升；最大字是帶一串-site:排除語法的簡體查詢(49曝光)，疑似工具/爬蟲查詢而非真人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gold-highlighter-trend-2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>趨勢分析</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>金色光感妝</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.79%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>排名4.4；CTR仍全站最高但曝光僅19，樣本小</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mask-usage-guide</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>敷面膜時間</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>91</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>曝光23→91、首次取得點擊；排名7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>concealer-stick-vs-liquid</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>遮瑕膏遮瑕液差別</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>低CTR懸案：本次3.85%(9/24為1.49%)，點擊1→2，曝光67→52；樣本小，再觀察一次才算改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>facial-cleanser-tightness-guide</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>洗面乳刺激緊繃</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>107</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>低CTR懸案，連續第5次追蹤在1%以下；可見查詢字為0，仍列下批標題優化候選</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cleansing-product-types-guide</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>卸妝產品種類</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>90</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>排名7.0；CTR 1.11%偏低，可見查詢字為0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lotion-layering-pilling</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>乳液搓泥</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cleansing-balm-review-2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>卸妝膏推薦</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>mask-review-2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>面膜推薦</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>hazy-eye-makeup-trend-2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>趨勢分析</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026眼妝趨勢</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>排名6.5，連續2次各1點擊</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cream-lotion-texture-guide</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>乳液乳霜差別</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>232</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>9/24選定的優化對象；206→232曝光仍0點擊，「乳液乳霜差別」集群主力字排20~38名。優化上線日期要對照異動記錄，窗口涵蓋天數不足前不做成效判斷</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eyeshadow-beginner-guide-2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>新手眼影教學</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>曝光113→99仍0點擊；「眼影教學」排27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lip-makeup-comparison</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>唇膏唇釉唇蜜差別</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>排名7.1在第1頁仍0點擊，維持下批標題優化候選</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dept-store-anniversary-beauty-central-2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>資訊懶人包</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>台中百貨週年慶</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>9/21上架，首次進榜(18曝光)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>primer-caking-whitecast</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>妝前乳卡粉</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>eye-cream-usage-guide</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>眼霜用法</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sunscreen-pilling-guide</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>防曬乳搓泥</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cleansing-oil-emulsify</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>卸妝油乳化</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>retinol-beginner-guide</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A醇怎麼用</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>9/23上架，首次進榜(5曝光)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>setting-method-comparison</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>蜜粉氣墊粉餅定妝噴霧比較</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9/1改標題後第4次追蹤，曝光13→4仍0點擊，維持「該次優化無效」判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>eyeliner-beginner-guide</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>眼線筆新手教學</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sunburn-mask-guide</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>曬後面膜推薦</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cushion-foundation-guide</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>氣墊粉餅推薦</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>曝光10→3，排名9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>foundation-seasonal-caking-guide</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>情境季節</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>粉底液卡紋</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>waterproof-summer-makeup</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>情境季節</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>夏天脫妝</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>blush-shade-guide</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>腮紅推薦</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>曝光19→3、頁面排名27.3，衰退持續，9/24列的「需查因」尚未處理</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>exfoliation-beginner-guide</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>去角質教學</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>serum-am-pm-guide</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>成分解析</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>早C晚A</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>bare-faced-makeup-2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>趨勢分析</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>偽素顏妝</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>toner-guide-2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>化妝水推薦</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lotion-mistakes-guide</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>同類比較</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>乳液推薦</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mascara-selection-guide</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>新手教學</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>睫毛膏怎麼選</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tired-glam-makeup-trend</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>趨勢分析</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>倦怠感妝容</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>